--- a/cook/high_freq_imaging/status_report.xlsx
+++ b/cook/high_freq_imaging/status_report.xlsx
@@ -573,7 +573,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFBCBD22"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -597,7 +597,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF9467BD"/>
+      <color rgb="FFBCBD22"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -606,14 +606,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF7F0E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -645,7 +637,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF2CA02C"/>
+      <color rgb="FFD62728"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -653,7 +645,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFD62728"/>
+      <color rgb="FF9467BD"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF2CA02C"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
